--- a/data/tableau_complet_sources.xlsx
+++ b/data/tableau_complet_sources.xlsx
@@ -157,10 +157,10 @@
     <t>Inserm 2021, présomption forte</t>
   </si>
   <si>
-    <t>Inserm 2021 (AGRICAN) ; piclorame 2026</t>
-  </si>
-  <si>
-    <t>Inserm 2021 ; thèse 2021 (OR=1,51 adulte)</t>
+    <t>Inserm 2021, AGRICAN ; piclorame 2026</t>
+  </si>
+  <si>
+    <t>Inserm 2021 ; thèse 2021, OR = 1,51 chez l'adulte</t>
   </si>
   <si>
     <t>Ligue contre le cancer ; JCO 2025</t>
@@ -184,19 +184,19 @@
     <t>ScienceDirect 2023, preuves limitées</t>
   </si>
   <si>
-    <t>Ligue contre le cancer (Inserm 2021)</t>
+    <t>Ligue contre le cancer, d'après Inserm 2021</t>
   </si>
   <si>
     <t>Non documenté</t>
   </si>
   <si>
-    <t>Données insuffisantes (Inserm)</t>
-  </si>
-  <si>
-    <t>Non documenté (vs LNH)</t>
-  </si>
-  <si>
-    <t>Données insuffisantes (ORL)</t>
+    <t>Données insuffisantes, Inserm</t>
+  </si>
+  <si>
+    <t>Non documenté, contrairement aux LNH</t>
+  </si>
+  <si>
+    <t>Données insuffisantes, cancers ORL</t>
   </si>
 </sst>
 </file>
@@ -585,7 +585,7 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>0.1347</v>
+        <v>0.2423</v>
       </c>
       <c r="E2" t="s">
         <v>44</v>
@@ -602,7 +602,7 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>0.5345</v>
+        <v>0.6344</v>
       </c>
       <c r="E3" t="s">
         <v>45</v>
@@ -619,7 +619,7 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>0.1588</v>
+        <v>0.0619</v>
       </c>
       <c r="E4" t="s">
         <v>44</v>
@@ -636,7 +636,7 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>0.6439</v>
+        <v>0.3924</v>
       </c>
       <c r="E5" t="s">
         <v>44</v>
@@ -653,7 +653,7 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>0.015</v>
+        <v>0.0346</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
@@ -670,7 +670,7 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>0.5492</v>
+        <v>0.7248</v>
       </c>
       <c r="E7" t="s">
         <v>44</v>
@@ -687,7 +687,7 @@
         <v>41</v>
       </c>
       <c r="D8">
-        <v>0.6435999999999999</v>
+        <v>0.2729</v>
       </c>
       <c r="E8" t="s">
         <v>44</v>
@@ -704,7 +704,7 @@
         <v>41</v>
       </c>
       <c r="D9">
-        <v>0.9782</v>
+        <v>0.9385</v>
       </c>
       <c r="E9" t="s">
         <v>44</v>
@@ -718,10 +718,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10">
-        <v>0.0446</v>
+        <v>0.1613</v>
       </c>
       <c r="E10" t="s">
         <v>46</v>
@@ -738,7 +738,7 @@
         <v>41</v>
       </c>
       <c r="D11">
-        <v>0.3324</v>
+        <v>0.4711</v>
       </c>
       <c r="E11" t="s">
         <v>46</v>
@@ -755,7 +755,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.2611</v>
+        <v>0.262</v>
       </c>
       <c r="E12" t="s">
         <v>45</v>
@@ -803,10 +803,10 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15">
-        <v>0.0598</v>
+        <v>0.0482</v>
       </c>
       <c r="E15" t="s">
         <v>49</v>
@@ -820,10 +820,10 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16">
-        <v>0.07539999999999999</v>
+        <v>0.0157</v>
       </c>
       <c r="E16" t="s">
         <v>50</v>
@@ -840,7 +840,7 @@
         <v>42</v>
       </c>
       <c r="D17">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
         <v>51</v>
@@ -857,7 +857,7 @@
         <v>42</v>
       </c>
       <c r="D18">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="E18" t="s">
         <v>52</v>
@@ -874,7 +874,7 @@
         <v>42</v>
       </c>
       <c r="D19">
-        <v>0.0121</v>
+        <v>0.0056</v>
       </c>
       <c r="E19" t="s">
         <v>53</v>
@@ -891,7 +891,7 @@
         <v>42</v>
       </c>
       <c r="D20">
-        <v>0.0214</v>
+        <v>0.0039</v>
       </c>
       <c r="E20" t="s">
         <v>54</v>
@@ -908,7 +908,7 @@
         <v>41</v>
       </c>
       <c r="D21">
-        <v>0.2034</v>
+        <v>0.3194</v>
       </c>
       <c r="E21" t="s">
         <v>55</v>
@@ -925,7 +925,7 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>0.0795</v>
+        <v>0.1078</v>
       </c>
       <c r="E22" t="s">
         <v>56</v>
@@ -942,7 +942,7 @@
         <v>41</v>
       </c>
       <c r="D23">
-        <v>0.6944</v>
+        <v>0.8202</v>
       </c>
       <c r="E23" t="s">
         <v>53</v>
@@ -959,7 +959,7 @@
         <v>41</v>
       </c>
       <c r="D24">
-        <v>0.4363</v>
+        <v>0.9519</v>
       </c>
       <c r="E24" t="s">
         <v>53</v>
@@ -976,7 +976,7 @@
         <v>41</v>
       </c>
       <c r="D25">
-        <v>0.0687</v>
+        <v>0.0508</v>
       </c>
       <c r="E25" t="s">
         <v>57</v>
@@ -993,7 +993,7 @@
         <v>43</v>
       </c>
       <c r="D26">
-        <v>0.0188</v>
+        <v>0.0465</v>
       </c>
       <c r="E26" t="s">
         <v>57</v>
@@ -1010,7 +1010,7 @@
         <v>43</v>
       </c>
       <c r="D27">
-        <v>0.0069</v>
+        <v>0.0176</v>
       </c>
       <c r="E27" t="s">
         <v>58</v>
@@ -1027,7 +1027,7 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>0.9676</v>
+        <v>0.8379</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
@@ -1044,7 +1044,7 @@
         <v>43</v>
       </c>
       <c r="D29">
-        <v>0.0156</v>
+        <v>0.0031</v>
       </c>
       <c r="E29" t="s">
         <v>57</v>
@@ -1061,7 +1061,7 @@
         <v>41</v>
       </c>
       <c r="D30">
-        <v>0.1108</v>
+        <v>0.0502</v>
       </c>
       <c r="E30" t="s">
         <v>57</v>
@@ -1075,10 +1075,10 @@
         <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31">
-        <v>0.0573</v>
+        <v>0.028</v>
       </c>
       <c r="E31" t="s">
         <v>59</v>
@@ -1095,7 +1095,7 @@
         <v>43</v>
       </c>
       <c r="D32">
-        <v>0.0042</v>
+        <v>0.0012</v>
       </c>
       <c r="E32" t="s">
         <v>60</v>
@@ -1112,7 +1112,7 @@
         <v>41</v>
       </c>
       <c r="D33">
-        <v>0.0507</v>
+        <v>0.0624</v>
       </c>
       <c r="E33" t="s">
         <v>58</v>
@@ -1129,7 +1129,7 @@
         <v>42</v>
       </c>
       <c r="D34">
-        <v>0.0018</v>
+        <v>0.0003</v>
       </c>
       <c r="E34" t="s">
         <v>57</v>
